--- a/artfynd/A 33518-2025 artfynd.xlsx
+++ b/artfynd/A 33518-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>73089118</v>
       </c>
       <c r="B2" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -731,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462675.1749548421</v>
+        <v>462675</v>
       </c>
       <c r="R2" t="n">
-        <v>6599261.163625563</v>
+        <v>6599261</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,19 +764,9 @@
           <t>2018-09-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-09-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
